--- a/Files/RAJDHANI NIGHT.xlsx
+++ b/Files/RAJDHANI NIGHT.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$525</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$527</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2612,6 +2612,12 @@
   </x:si>
   <x:si>
     <x:t>31/08/2026 to 04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 11/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 18/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -3067,7 +3073,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V525"/>
+  <x:dimension ref="A1:V527"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -38720,40 +38726,40 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="N525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="O525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="P525" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="Q525" s="3" t="s">
         <x:v>37</x:v>
@@ -38774,8 +38780,144 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
+    <x:row r="526" spans="1:22">
+      <x:c r="A526" s="3" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="B526" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C526" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D526" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E526" s="3" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F526" s="3" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G526" s="3" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H526" s="3" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="I526" s="3" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="J526" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K526" s="3" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="L526" s="3" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="M526" s="3" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="N526" s="3" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="O526" s="3" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="P526" s="3" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="Q526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="T526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V526" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:22">
+      <x:c r="A527" s="3" t="s">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="B527" s="3" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C527" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D527" s="3" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="E527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="T527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V527" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V525"/>
+  <x:autoFilter ref="A1:V527"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -38798,39 +38940,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>865</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>866</x:v>
+        <x:v>868</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>867</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>868</x:v>
+        <x:v>870</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>869</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>870</x:v>
+        <x:v>872</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>871</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>524</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>872</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -38838,10 +38980,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>873</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>864</x:v>
+        <x:v>866</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/RAJDHANI NIGHT.xlsx
+++ b/Files/RAJDHANI NIGHT.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$527</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$528</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2618,6 +2618,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 25/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -3073,7 +3076,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V527"/>
+  <x:dimension ref="A1:V528"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -38862,40 +38865,40 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="E527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="G527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="J527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="L527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="N527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="O527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="P527" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="Q527" s="3" t="s">
         <x:v>37</x:v>
@@ -38916,8 +38919,76 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
+    <x:row r="528" spans="1:22">
+      <x:c r="A528" s="3" t="s">
+        <x:v>867</x:v>
+      </x:c>
+      <x:c r="B528" s="3" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="C528" s="3" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D528" s="3" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="E528" s="3" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F528" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G528" s="3" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H528" s="3" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="I528" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J528" s="3" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K528" s="3" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="L528" s="3" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="M528" s="3" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="N528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="T528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V528" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V527"/>
+  <x:autoFilter ref="A1:V528"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -38940,39 +39011,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>867</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>868</x:v>
+        <x:v>869</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>869</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>870</x:v>
+        <x:v>871</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>871</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>872</x:v>
+        <x:v>873</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>873</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>874</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -38980,10 +39051,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>875</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>866</x:v>
+        <x:v>867</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
